--- a/docs/mapa.xlsx
+++ b/docs/mapa.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Data\Laravel_Dev\Examen-Grado\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FA11C7-3C23-41AD-9A14-539C9CA17F99}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7B0BB3-0339-4DE0-93F9-8EB3E683CA10}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos para Mapa" sheetId="1" r:id="rId1"/>
     <sheet name="Datos para Mapa - M" sheetId="2" r:id="rId2"/>
+    <sheet name="Datos para Mapa - A" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="36">
   <si>
     <t>DATOS DE ELABORACIÓN</t>
   </si>
@@ -122,6 +123,18 @@
   </si>
   <si>
     <t>S/N</t>
+  </si>
+  <si>
+    <t>Alexander Claure Jimenez</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 17°51'34.26"S</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 63°13'59.39"O</t>
   </si>
 </sst>
 </file>
@@ -455,6 +468,108 @@
         <a:xfrm>
           <a:off x="3771900" y="1619250"/>
           <a:ext cx="2143125" cy="2143125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5B0143E-E8AB-4A57-97CF-ABFD69BFB410}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4362450" y="3838575"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>43142</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1903175</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E0387D4-1A4F-402A-971F-A65C2967264B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3771900" y="1976717"/>
+          <a:ext cx="2493725" cy="1661833"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1017,4 +1132,150 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72093589-71BE-45EE-817B-1F9A5CDBFB22}">
+  <dimension ref="F3:M17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="32.140625" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="14"/>
+      <c r="I3" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="6:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="6:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="4">
+        <v>96135</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="F6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I9" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I14" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="19"/>
+    </row>
+    <row r="15" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="6:13" x14ac:dyDescent="0.25">
+      <c r="I16" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I17" s="11"/>
+      <c r="J17" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I14:J14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>